--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0886</v>
+        <v>0.5078</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9114</v>
+        <v>0.4922</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -11269,10 +11269,10 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>0.6274</v>
+        <v>0.6198</v>
       </c>
       <c r="J119" t="n">
-        <v>0.3726</v>
+        <v>0.3802</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -19661,10 +19661,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0886</v>
+        <v>0.5078</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9114</v>
+        <v>0.4922</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -25821,10 +25821,10 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>0.6274</v>
+        <v>0.6198</v>
       </c>
       <c r="J119" t="n">
-        <v>0.3726</v>
+        <v>0.3802</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5078</v>
+        <v>0.5157</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4922</v>
+        <v>0.4843</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -11269,10 +11269,10 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>0.6198</v>
+        <v>0.677</v>
       </c>
       <c r="J119" t="n">
-        <v>0.3802</v>
+        <v>0.323</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -19661,10 +19661,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5078</v>
+        <v>0.5157</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4922</v>
+        <v>0.4843</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -25821,10 +25821,10 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>0.6198</v>
+        <v>0.677</v>
       </c>
       <c r="J119" t="n">
-        <v>0.3802</v>
+        <v>0.323</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9737,10 +9737,10 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>0.1482</v>
+        <v>0.4209</v>
       </c>
       <c r="J98" t="n">
-        <v>0.8518</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9821,10 +9821,10 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>0.1482</v>
+        <v>0.4209</v>
       </c>
       <c r="J99" t="n">
-        <v>0.8518</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24289,10 +24289,10 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>0.1482</v>
+        <v>0.4209</v>
       </c>
       <c r="J98" t="n">
-        <v>0.8518</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24373,10 +24373,10 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>0.1482</v>
+        <v>0.4209</v>
       </c>
       <c r="J99" t="n">
-        <v>0.8518</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -7937,10 +7937,10 @@
         <v>0.835</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1716</v>
+        <v>0.4401</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8284</v>
+        <v>0.5599</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -8349,10 +8349,10 @@
         <v>0.84</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1716</v>
+        <v>0.4401</v>
       </c>
       <c r="J83" t="n">
-        <v>0.8284</v>
+        <v>0.5599</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -22489,10 +22489,10 @@
         <v>0.835</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1716</v>
+        <v>0.4401</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8284</v>
+        <v>0.5599</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -22901,10 +22901,10 @@
         <v>0.84</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1716</v>
+        <v>0.4401</v>
       </c>
       <c r="J83" t="n">
-        <v>0.8284</v>
+        <v>0.5599</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -10193,10 +10193,10 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>0.8796</v>
+        <v>0.6863</v>
       </c>
       <c r="J104" t="n">
-        <v>0.1204</v>
+        <v>0.3137</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -14769,10 +14769,10 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
-        <v>0.6044</v>
+        <v>0.6962</v>
       </c>
       <c r="J168" t="n">
-        <v>0.3956</v>
+        <v>0.3038</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -24745,10 +24745,10 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>0.8796</v>
+        <v>0.6863</v>
       </c>
       <c r="J104" t="n">
-        <v>0.1204</v>
+        <v>0.3137</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -29257,10 +29257,10 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
-        <v>0.6044</v>
+        <v>0.6962</v>
       </c>
       <c r="J167" t="n">
-        <v>0.3956</v>
+        <v>0.3038</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/backtest.xlsx
+++ b/backtest.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
